--- a/uploads/excel_format/bulk upload format.xlsx
+++ b/uploads/excel_format/bulk upload format.xlsx
@@ -1,22 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\Marudham\uploads\excel_format\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4507"/>
+  <workbookPr/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12435"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <calcPr calcId="125725"/>
+  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -24,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="146">
   <si>
     <t>Sl.no</t>
   </si>
@@ -450,16 +445,28 @@
   </si>
   <si>
     <t>D1</t>
+  </si>
+  <si>
+    <t>Document Status</t>
+  </si>
+  <si>
+    <t>YES</t>
+  </si>
+  <si>
+    <t>Document Remark</t>
+  </si>
+  <si>
+    <t>xxx</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-14009]yyyy/mm/dd;@"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -478,6 +485,12 @@
       <color rgb="FF333333"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -506,7 +519,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -523,6 +536,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -583,7 +597,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -618,7 +632,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -795,16 +809,16 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:CS13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:CU13"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.28515625" bestFit="1" customWidth="1"/>
@@ -865,44 +879,45 @@
     <col min="58" max="58" width="9.28515625" bestFit="1" customWidth="1"/>
     <col min="59" max="59" width="17.42578125" bestFit="1" customWidth="1"/>
     <col min="60" max="60" width="21" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="11" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="14" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="8" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="11" bestFit="1" customWidth="1"/>
-    <col min="71" max="71" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="72" max="72" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="73" max="73" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="74" max="74" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="75" max="75" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="76" max="76" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="77" max="77" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="78" max="79" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="80" max="80" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="81" max="81" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="82" max="82" width="18" bestFit="1" customWidth="1"/>
-    <col min="83" max="83" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="84" max="84" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="85" max="85" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="86" max="86" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="87" max="87" width="12" bestFit="1" customWidth="1"/>
-    <col min="88" max="88" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="89" max="89" width="14" bestFit="1" customWidth="1"/>
-    <col min="90" max="90" width="6" bestFit="1" customWidth="1"/>
-    <col min="91" max="91" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="92" max="92" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="93" max="93" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="94" max="94" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="95" max="96" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="97" max="97" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="61" max="62" width="21" customWidth="1"/>
+    <col min="63" max="63" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="11" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="14" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="8" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="11" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="80" max="81" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="82" max="82" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="83" max="83" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="84" max="84" width="18" bestFit="1" customWidth="1"/>
+    <col min="85" max="85" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="86" max="86" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="87" max="87" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="88" max="88" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="89" max="89" width="12" bestFit="1" customWidth="1"/>
+    <col min="90" max="90" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="91" max="91" width="14" bestFit="1" customWidth="1"/>
+    <col min="92" max="92" width="6" bestFit="1" customWidth="1"/>
+    <col min="93" max="93" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="94" max="94" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="95" max="95" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="96" max="96" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="97" max="98" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="99" max="99" width="11.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:97" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:99" s="9" customFormat="1">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -1084,118 +1099,124 @@
         <v>59</v>
       </c>
       <c r="BI1" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="BJ1" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="BK1" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="BJ1" s="9" t="s">
+      <c r="BL1" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="BK1" s="9" t="s">
+      <c r="BM1" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="BL1" s="9" t="s">
+      <c r="BN1" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="BM1" s="9" t="s">
+      <c r="BO1" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="BN1" s="9" t="s">
+      <c r="BP1" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="BO1" s="9" t="s">
+      <c r="BQ1" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="BP1" s="9" t="s">
+      <c r="BR1" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="BQ1" s="9" t="s">
+      <c r="BS1" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="BR1" s="9" t="s">
+      <c r="BT1" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="BS1" s="9" t="s">
+      <c r="BU1" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="BT1" s="9" t="s">
+      <c r="BV1" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="BU1" s="9" t="s">
+      <c r="BW1" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="BV1" s="9" t="s">
+      <c r="BX1" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="BW1" s="9" t="s">
+      <c r="BY1" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="BX1" s="9" t="s">
+      <c r="BZ1" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="BY1" s="9" t="s">
+      <c r="CA1" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="BZ1" s="9" t="s">
+      <c r="CB1" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="CA1" s="9" t="s">
+      <c r="CC1" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="CB1" s="9" t="s">
+      <c r="CD1" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="CC1" s="9" t="s">
+      <c r="CE1" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="CD1" s="9" t="s">
+      <c r="CF1" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="CE1" s="9" t="s">
+      <c r="CG1" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="CF1" s="9" t="s">
+      <c r="CH1" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="CG1" s="9" t="s">
+      <c r="CI1" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="CH1" s="9" t="s">
+      <c r="CJ1" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="CI1" s="9" t="s">
+      <c r="CK1" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="CJ1" s="9" t="s">
+      <c r="CL1" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="CK1" s="9" t="s">
+      <c r="CM1" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="CL1" s="9" t="s">
+      <c r="CN1" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="CM1" s="9" t="s">
+      <c r="CO1" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="CN1" s="9" t="s">
+      <c r="CP1" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="CO1" s="9" t="s">
+      <c r="CQ1" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="CP1" s="9" t="s">
+      <c r="CR1" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="CQ1" s="9" t="s">
+      <c r="CS1" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="CR1" s="9" t="s">
+      <c r="CT1" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="CS1" s="9" t="s">
+      <c r="CU1" s="9" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="2" spans="1:97" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:99" ht="15.75">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1370,115 +1391,121 @@
       <c r="BH2" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="BI2" s="2">
+      <c r="BI2" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="BJ2" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="BK2" s="2">
         <v>45238</v>
       </c>
-      <c r="BJ2" s="1" t="s">
+      <c r="BL2" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="BK2" s="1" t="s">
+      <c r="BM2" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="BL2" s="1" t="s">
+      <c r="BN2" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="BM2" s="1" t="s">
+      <c r="BO2" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="BN2" s="4"/>
-      <c r="BO2" s="4"/>
-      <c r="BP2" s="1">
+      <c r="BP2" s="4"/>
+      <c r="BQ2" s="4"/>
+      <c r="BR2" s="1">
         <v>2</v>
       </c>
-      <c r="BQ2" s="1">
+      <c r="BS2" s="1">
         <v>6</v>
       </c>
-      <c r="BR2" s="4">
+      <c r="BT2" s="4">
         <v>2</v>
       </c>
-      <c r="BS2" s="1">
+      <c r="BU2" s="1">
         <v>0</v>
       </c>
-      <c r="BT2" s="1">
+      <c r="BV2" s="1">
         <v>15000</v>
       </c>
-      <c r="BU2" s="1">
+      <c r="BW2" s="1">
         <v>15000</v>
       </c>
-      <c r="BV2" s="7">
+      <c r="BX2" s="7">
         <v>1800</v>
       </c>
-      <c r="BW2" s="7">
+      <c r="BY2" s="7">
         <v>16800</v>
       </c>
-      <c r="BX2" s="1">
+      <c r="BZ2" s="1">
         <v>2800</v>
       </c>
-      <c r="BY2" s="7">
+      <c r="CA2" s="7">
         <v>300</v>
       </c>
-      <c r="BZ2" s="4">
+      <c r="CB2" s="4">
         <v>0</v>
       </c>
-      <c r="CA2" s="7">
+      <c r="CC2" s="7">
         <v>14700</v>
       </c>
-      <c r="CB2" s="2">
+      <c r="CD2" s="2">
         <v>45270</v>
       </c>
-      <c r="CC2" s="2">
+      <c r="CE2" s="2">
         <v>45422</v>
       </c>
-      <c r="CD2" s="1" t="s">
+      <c r="CF2" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="CE2" s="1" t="s">
+      <c r="CG2" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="CF2" s="3">
+      <c r="CH2" s="3">
         <v>239903777436</v>
       </c>
-      <c r="CG2" s="1" t="s">
+      <c r="CI2" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="CH2" s="5" t="s">
+      <c r="CJ2" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="CI2" s="6" t="s">
+      <c r="CK2" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="CJ2" s="1" t="s">
+      <c r="CL2" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="CK2" s="1" t="s">
+      <c r="CM2" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="CL2" s="7">
+      <c r="CN2" s="7">
         <v>14700</v>
       </c>
-      <c r="CM2" s="4">
+      <c r="CO2" s="4">
         <v>0</v>
       </c>
-      <c r="CN2" s="3">
+      <c r="CP2" s="3">
         <v>239903777436</v>
       </c>
-      <c r="CO2" s="1" t="s">
+      <c r="CQ2" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="CP2" t="s">
+      <c r="CR2" t="s">
         <v>135</v>
       </c>
-      <c r="CQ2" t="s">
+      <c r="CS2" t="s">
         <v>136</v>
       </c>
-      <c r="CR2" t="s">
+      <c r="CT2" t="s">
         <v>137</v>
       </c>
-      <c r="CS2" s="2">
+      <c r="CU2" s="2">
         <v>45483</v>
       </c>
     </row>
-    <row r="3" spans="1:97" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:99">
       <c r="A3" s="1"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3"/>
@@ -1539,36 +1566,38 @@
       <c r="BF3" s="4"/>
       <c r="BG3" s="1"/>
       <c r="BH3" s="1"/>
-      <c r="BI3" s="2"/>
+      <c r="BI3" s="1"/>
       <c r="BJ3" s="1"/>
-      <c r="BK3" s="1"/>
+      <c r="BK3" s="2"/>
       <c r="BL3" s="1"/>
       <c r="BM3" s="1"/>
-      <c r="BN3" s="4"/>
-      <c r="BO3" s="4"/>
-      <c r="BP3" s="1"/>
-      <c r="BQ3" s="1"/>
-      <c r="BR3" s="4"/>
+      <c r="BN3" s="1"/>
+      <c r="BO3" s="1"/>
+      <c r="BP3" s="4"/>
+      <c r="BQ3" s="4"/>
+      <c r="BR3" s="1"/>
       <c r="BS3" s="1"/>
-      <c r="BT3" s="1"/>
+      <c r="BT3" s="4"/>
       <c r="BU3" s="1"/>
-      <c r="BX3" s="1"/>
-      <c r="BZ3" s="4"/>
-      <c r="CB3" s="2"/>
-      <c r="CC3" s="2"/>
-      <c r="CD3" s="1"/>
-      <c r="CE3" s="1"/>
-      <c r="CF3" s="3"/>
+      <c r="BV3" s="1"/>
+      <c r="BW3" s="1"/>
+      <c r="BZ3" s="1"/>
+      <c r="CB3" s="4"/>
+      <c r="CD3" s="2"/>
+      <c r="CE3" s="2"/>
+      <c r="CF3" s="1"/>
       <c r="CG3" s="1"/>
-      <c r="CH3" s="8"/>
-      <c r="CI3" s="6"/>
-      <c r="CJ3" s="1"/>
-      <c r="CK3" s="1"/>
-      <c r="CM3" s="4"/>
-      <c r="CN3" s="3"/>
-      <c r="CO3" s="1"/>
+      <c r="CH3" s="3"/>
+      <c r="CI3" s="1"/>
+      <c r="CJ3" s="8"/>
+      <c r="CK3" s="6"/>
+      <c r="CL3" s="1"/>
+      <c r="CM3" s="1"/>
+      <c r="CO3" s="4"/>
+      <c r="CP3" s="3"/>
+      <c r="CQ3" s="1"/>
     </row>
-    <row r="4" spans="1:97" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:99">
       <c r="A4" s="1"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3"/>
@@ -1629,36 +1658,38 @@
       <c r="BF4" s="4"/>
       <c r="BG4" s="1"/>
       <c r="BH4" s="1"/>
-      <c r="BI4" s="2"/>
+      <c r="BI4" s="1"/>
       <c r="BJ4" s="1"/>
-      <c r="BK4" s="1"/>
+      <c r="BK4" s="2"/>
       <c r="BL4" s="1"/>
       <c r="BM4" s="1"/>
-      <c r="BN4" s="4"/>
-      <c r="BO4" s="4"/>
-      <c r="BP4" s="1"/>
-      <c r="BQ4" s="1"/>
-      <c r="BR4" s="4"/>
+      <c r="BN4" s="1"/>
+      <c r="BO4" s="1"/>
+      <c r="BP4" s="4"/>
+      <c r="BQ4" s="4"/>
+      <c r="BR4" s="1"/>
       <c r="BS4" s="1"/>
-      <c r="BT4" s="1"/>
+      <c r="BT4" s="4"/>
       <c r="BU4" s="1"/>
-      <c r="BX4" s="1"/>
-      <c r="BZ4" s="4"/>
-      <c r="CB4" s="2"/>
-      <c r="CC4" s="2"/>
-      <c r="CD4" s="1"/>
-      <c r="CE4" s="1"/>
-      <c r="CF4" s="3"/>
+      <c r="BV4" s="1"/>
+      <c r="BW4" s="1"/>
+      <c r="BZ4" s="1"/>
+      <c r="CB4" s="4"/>
+      <c r="CD4" s="2"/>
+      <c r="CE4" s="2"/>
+      <c r="CF4" s="1"/>
       <c r="CG4" s="1"/>
-      <c r="CH4" s="8"/>
-      <c r="CI4" s="6"/>
-      <c r="CJ4" s="1"/>
-      <c r="CK4" s="1"/>
-      <c r="CM4" s="4"/>
-      <c r="CN4" s="3"/>
-      <c r="CO4" s="1"/>
+      <c r="CH4" s="3"/>
+      <c r="CI4" s="1"/>
+      <c r="CJ4" s="8"/>
+      <c r="CK4" s="6"/>
+      <c r="CL4" s="1"/>
+      <c r="CM4" s="1"/>
+      <c r="CO4" s="4"/>
+      <c r="CP4" s="3"/>
+      <c r="CQ4" s="1"/>
     </row>
-    <row r="5" spans="1:97" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:99">
       <c r="A5" s="1"/>
       <c r="B5" s="2"/>
       <c r="C5" s="3"/>
@@ -1719,36 +1750,38 @@
       <c r="BF5" s="4"/>
       <c r="BG5" s="1"/>
       <c r="BH5" s="1"/>
-      <c r="BI5" s="2"/>
+      <c r="BI5" s="1"/>
       <c r="BJ5" s="1"/>
-      <c r="BK5" s="1"/>
+      <c r="BK5" s="2"/>
       <c r="BL5" s="1"/>
       <c r="BM5" s="1"/>
-      <c r="BN5" s="4"/>
-      <c r="BO5" s="4"/>
-      <c r="BP5" s="1"/>
-      <c r="BQ5" s="1"/>
-      <c r="BR5" s="4"/>
+      <c r="BN5" s="1"/>
+      <c r="BO5" s="1"/>
+      <c r="BP5" s="4"/>
+      <c r="BQ5" s="4"/>
+      <c r="BR5" s="1"/>
       <c r="BS5" s="1"/>
-      <c r="BT5" s="1"/>
+      <c r="BT5" s="4"/>
       <c r="BU5" s="1"/>
-      <c r="BX5" s="1"/>
-      <c r="BZ5" s="4"/>
-      <c r="CB5" s="2"/>
-      <c r="CC5" s="2"/>
-      <c r="CD5" s="1"/>
-      <c r="CE5" s="1"/>
-      <c r="CF5" s="3"/>
+      <c r="BV5" s="1"/>
+      <c r="BW5" s="1"/>
+      <c r="BZ5" s="1"/>
+      <c r="CB5" s="4"/>
+      <c r="CD5" s="2"/>
+      <c r="CE5" s="2"/>
+      <c r="CF5" s="1"/>
       <c r="CG5" s="1"/>
-      <c r="CH5" s="8"/>
-      <c r="CI5" s="6"/>
-      <c r="CJ5" s="1"/>
-      <c r="CK5" s="1"/>
-      <c r="CM5" s="4"/>
-      <c r="CN5" s="3"/>
-      <c r="CO5" s="1"/>
+      <c r="CH5" s="3"/>
+      <c r="CI5" s="1"/>
+      <c r="CJ5" s="8"/>
+      <c r="CK5" s="6"/>
+      <c r="CL5" s="1"/>
+      <c r="CM5" s="1"/>
+      <c r="CO5" s="4"/>
+      <c r="CP5" s="3"/>
+      <c r="CQ5" s="1"/>
     </row>
-    <row r="6" spans="1:97" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:99">
       <c r="A6" s="1"/>
       <c r="B6" s="2"/>
       <c r="C6" s="3"/>
@@ -1809,35 +1842,37 @@
       <c r="BF6" s="4"/>
       <c r="BG6" s="1"/>
       <c r="BH6" s="1"/>
-      <c r="BI6" s="2"/>
+      <c r="BI6" s="1"/>
       <c r="BJ6" s="1"/>
-      <c r="BK6" s="1"/>
+      <c r="BK6" s="2"/>
       <c r="BL6" s="1"/>
       <c r="BM6" s="1"/>
-      <c r="BN6" s="4"/>
-      <c r="BO6" s="4"/>
-      <c r="BP6" s="1"/>
-      <c r="BQ6" s="1"/>
+      <c r="BN6" s="1"/>
+      <c r="BO6" s="1"/>
+      <c r="BP6" s="4"/>
+      <c r="BQ6" s="4"/>
+      <c r="BR6" s="1"/>
       <c r="BS6" s="1"/>
-      <c r="BT6" s="1"/>
       <c r="BU6" s="1"/>
-      <c r="BX6" s="1"/>
-      <c r="BZ6" s="4"/>
-      <c r="CB6" s="2"/>
-      <c r="CC6" s="2"/>
-      <c r="CD6" s="1"/>
-      <c r="CE6" s="1"/>
-      <c r="CF6" s="3"/>
+      <c r="BV6" s="1"/>
+      <c r="BW6" s="1"/>
+      <c r="BZ6" s="1"/>
+      <c r="CB6" s="4"/>
+      <c r="CD6" s="2"/>
+      <c r="CE6" s="2"/>
+      <c r="CF6" s="1"/>
       <c r="CG6" s="1"/>
-      <c r="CH6" s="8"/>
-      <c r="CI6" s="6"/>
-      <c r="CJ6" s="1"/>
-      <c r="CK6" s="1"/>
-      <c r="CM6" s="4"/>
-      <c r="CN6" s="3"/>
-      <c r="CO6" s="1"/>
+      <c r="CH6" s="3"/>
+      <c r="CI6" s="1"/>
+      <c r="CJ6" s="8"/>
+      <c r="CK6" s="6"/>
+      <c r="CL6" s="1"/>
+      <c r="CM6" s="1"/>
+      <c r="CO6" s="4"/>
+      <c r="CP6" s="3"/>
+      <c r="CQ6" s="1"/>
     </row>
-    <row r="7" spans="1:97" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:99">
       <c r="A7" s="1"/>
       <c r="B7" s="2"/>
       <c r="C7" s="3"/>
@@ -1898,35 +1933,37 @@
       <c r="BF7" s="4"/>
       <c r="BG7" s="1"/>
       <c r="BH7" s="1"/>
-      <c r="BI7" s="2"/>
+      <c r="BI7" s="1"/>
       <c r="BJ7" s="1"/>
-      <c r="BK7" s="1"/>
+      <c r="BK7" s="2"/>
       <c r="BL7" s="1"/>
       <c r="BM7" s="1"/>
-      <c r="BN7" s="4"/>
-      <c r="BO7" s="4"/>
-      <c r="BP7" s="1"/>
-      <c r="BQ7" s="1"/>
+      <c r="BN7" s="1"/>
+      <c r="BO7" s="1"/>
+      <c r="BP7" s="4"/>
+      <c r="BQ7" s="4"/>
+      <c r="BR7" s="1"/>
       <c r="BS7" s="1"/>
-      <c r="BT7" s="1"/>
       <c r="BU7" s="1"/>
-      <c r="BX7" s="1"/>
-      <c r="BZ7" s="4"/>
-      <c r="CB7" s="2"/>
-      <c r="CC7" s="2"/>
-      <c r="CD7" s="1"/>
-      <c r="CE7" s="1"/>
-      <c r="CF7" s="3"/>
+      <c r="BV7" s="1"/>
+      <c r="BW7" s="1"/>
+      <c r="BZ7" s="1"/>
+      <c r="CB7" s="4"/>
+      <c r="CD7" s="2"/>
+      <c r="CE7" s="2"/>
+      <c r="CF7" s="1"/>
       <c r="CG7" s="1"/>
-      <c r="CH7" s="8"/>
-      <c r="CI7" s="6"/>
-      <c r="CJ7" s="1"/>
-      <c r="CK7" s="1"/>
-      <c r="CM7" s="4"/>
-      <c r="CN7" s="3"/>
-      <c r="CO7" s="1"/>
+      <c r="CH7" s="3"/>
+      <c r="CI7" s="1"/>
+      <c r="CJ7" s="8"/>
+      <c r="CK7" s="6"/>
+      <c r="CL7" s="1"/>
+      <c r="CM7" s="1"/>
+      <c r="CO7" s="4"/>
+      <c r="CP7" s="3"/>
+      <c r="CQ7" s="1"/>
     </row>
-    <row r="8" spans="1:97" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:99">
       <c r="A8" s="1"/>
       <c r="B8" s="2"/>
       <c r="C8" s="3"/>
@@ -1987,35 +2024,37 @@
       <c r="BF8" s="4"/>
       <c r="BG8" s="1"/>
       <c r="BH8" s="1"/>
-      <c r="BI8" s="2"/>
+      <c r="BI8" s="1"/>
       <c r="BJ8" s="1"/>
-      <c r="BK8" s="1"/>
+      <c r="BK8" s="2"/>
       <c r="BL8" s="1"/>
       <c r="BM8" s="1"/>
-      <c r="BN8" s="4"/>
-      <c r="BO8" s="4"/>
-      <c r="BP8" s="1"/>
-      <c r="BQ8" s="1"/>
+      <c r="BN8" s="1"/>
+      <c r="BO8" s="1"/>
+      <c r="BP8" s="4"/>
+      <c r="BQ8" s="4"/>
+      <c r="BR8" s="1"/>
       <c r="BS8" s="1"/>
-      <c r="BT8" s="1"/>
       <c r="BU8" s="1"/>
-      <c r="BX8" s="1"/>
-      <c r="BZ8" s="4"/>
-      <c r="CB8" s="2"/>
-      <c r="CC8" s="2"/>
-      <c r="CD8" s="1"/>
-      <c r="CE8" s="1"/>
-      <c r="CF8" s="3"/>
+      <c r="BV8" s="1"/>
+      <c r="BW8" s="1"/>
+      <c r="BZ8" s="1"/>
+      <c r="CB8" s="4"/>
+      <c r="CD8" s="2"/>
+      <c r="CE8" s="2"/>
+      <c r="CF8" s="1"/>
       <c r="CG8" s="1"/>
-      <c r="CH8" s="8"/>
-      <c r="CI8" s="6"/>
-      <c r="CJ8" s="1"/>
-      <c r="CK8" s="1"/>
-      <c r="CM8" s="4"/>
-      <c r="CN8" s="3"/>
-      <c r="CO8" s="1"/>
+      <c r="CH8" s="3"/>
+      <c r="CI8" s="1"/>
+      <c r="CJ8" s="8"/>
+      <c r="CK8" s="6"/>
+      <c r="CL8" s="1"/>
+      <c r="CM8" s="1"/>
+      <c r="CO8" s="4"/>
+      <c r="CP8" s="3"/>
+      <c r="CQ8" s="1"/>
     </row>
-    <row r="9" spans="1:97" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:99">
       <c r="A9" s="1"/>
       <c r="B9" s="2"/>
       <c r="C9" s="3"/>
@@ -2076,35 +2115,37 @@
       <c r="BF9" s="4"/>
       <c r="BG9" s="1"/>
       <c r="BH9" s="1"/>
-      <c r="BI9" s="2"/>
+      <c r="BI9" s="1"/>
       <c r="BJ9" s="1"/>
-      <c r="BK9" s="1"/>
+      <c r="BK9" s="2"/>
       <c r="BL9" s="1"/>
       <c r="BM9" s="1"/>
-      <c r="BN9" s="4"/>
-      <c r="BO9" s="4"/>
-      <c r="BP9" s="1"/>
-      <c r="BQ9" s="1"/>
+      <c r="BN9" s="1"/>
+      <c r="BO9" s="1"/>
+      <c r="BP9" s="4"/>
+      <c r="BQ9" s="4"/>
+      <c r="BR9" s="1"/>
       <c r="BS9" s="1"/>
-      <c r="BT9" s="1"/>
       <c r="BU9" s="1"/>
-      <c r="BX9" s="1"/>
-      <c r="BZ9" s="4"/>
-      <c r="CB9" s="2"/>
-      <c r="CC9" s="2"/>
-      <c r="CD9" s="1"/>
-      <c r="CE9" s="1"/>
-      <c r="CF9" s="3"/>
+      <c r="BV9" s="1"/>
+      <c r="BW9" s="1"/>
+      <c r="BZ9" s="1"/>
+      <c r="CB9" s="4"/>
+      <c r="CD9" s="2"/>
+      <c r="CE9" s="2"/>
+      <c r="CF9" s="1"/>
       <c r="CG9" s="1"/>
-      <c r="CH9" s="8"/>
-      <c r="CI9" s="6"/>
-      <c r="CJ9" s="1"/>
-      <c r="CK9" s="1"/>
-      <c r="CM9" s="4"/>
-      <c r="CN9" s="3"/>
-      <c r="CO9" s="1"/>
+      <c r="CH9" s="3"/>
+      <c r="CI9" s="1"/>
+      <c r="CJ9" s="8"/>
+      <c r="CK9" s="6"/>
+      <c r="CL9" s="1"/>
+      <c r="CM9" s="1"/>
+      <c r="CO9" s="4"/>
+      <c r="CP9" s="3"/>
+      <c r="CQ9" s="1"/>
     </row>
-    <row r="10" spans="1:97" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:99">
       <c r="A10" s="1"/>
       <c r="B10" s="2"/>
       <c r="C10" s="3"/>
@@ -2165,36 +2206,38 @@
       <c r="BF10" s="4"/>
       <c r="BG10" s="1"/>
       <c r="BH10" s="1"/>
-      <c r="BI10" s="2"/>
+      <c r="BI10" s="1"/>
       <c r="BJ10" s="1"/>
-      <c r="BK10" s="1"/>
+      <c r="BK10" s="2"/>
       <c r="BL10" s="1"/>
       <c r="BM10" s="1"/>
-      <c r="BN10" s="4"/>
-      <c r="BO10" s="4"/>
-      <c r="BP10" s="1"/>
-      <c r="BQ10" s="1"/>
-      <c r="BR10" s="4"/>
+      <c r="BN10" s="1"/>
+      <c r="BO10" s="1"/>
+      <c r="BP10" s="4"/>
+      <c r="BQ10" s="4"/>
+      <c r="BR10" s="1"/>
       <c r="BS10" s="1"/>
-      <c r="BT10" s="1"/>
+      <c r="BT10" s="4"/>
       <c r="BU10" s="1"/>
-      <c r="BX10" s="1"/>
-      <c r="BZ10" s="4"/>
-      <c r="CB10" s="2"/>
-      <c r="CC10" s="2"/>
-      <c r="CD10" s="1"/>
-      <c r="CE10" s="1"/>
-      <c r="CF10" s="3"/>
+      <c r="BV10" s="1"/>
+      <c r="BW10" s="1"/>
+      <c r="BZ10" s="1"/>
+      <c r="CB10" s="4"/>
+      <c r="CD10" s="2"/>
+      <c r="CE10" s="2"/>
+      <c r="CF10" s="1"/>
       <c r="CG10" s="1"/>
-      <c r="CH10" s="8"/>
-      <c r="CI10" s="4"/>
-      <c r="CJ10" s="1"/>
-      <c r="CK10" s="1"/>
-      <c r="CM10" s="4"/>
-      <c r="CN10" s="3"/>
-      <c r="CO10" s="1"/>
+      <c r="CH10" s="3"/>
+      <c r="CI10" s="1"/>
+      <c r="CJ10" s="8"/>
+      <c r="CK10" s="4"/>
+      <c r="CL10" s="1"/>
+      <c r="CM10" s="1"/>
+      <c r="CO10" s="4"/>
+      <c r="CP10" s="3"/>
+      <c r="CQ10" s="1"/>
     </row>
-    <row r="11" spans="1:97" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:99">
       <c r="A11" s="1"/>
       <c r="B11" s="2"/>
       <c r="C11" s="3"/>
@@ -2255,36 +2298,38 @@
       <c r="BF11" s="4"/>
       <c r="BG11" s="1"/>
       <c r="BH11" s="1"/>
-      <c r="BI11" s="2"/>
+      <c r="BI11" s="1"/>
       <c r="BJ11" s="1"/>
-      <c r="BK11" s="1"/>
+      <c r="BK11" s="2"/>
       <c r="BL11" s="1"/>
       <c r="BM11" s="1"/>
-      <c r="BN11" s="4"/>
-      <c r="BO11" s="4"/>
-      <c r="BP11" s="1"/>
-      <c r="BQ11" s="1"/>
-      <c r="BR11" s="4"/>
+      <c r="BN11" s="1"/>
+      <c r="BO11" s="1"/>
+      <c r="BP11" s="4"/>
+      <c r="BQ11" s="4"/>
+      <c r="BR11" s="1"/>
       <c r="BS11" s="1"/>
-      <c r="BT11" s="1"/>
+      <c r="BT11" s="4"/>
       <c r="BU11" s="1"/>
-      <c r="BX11" s="1"/>
-      <c r="BZ11" s="4"/>
-      <c r="CB11" s="2"/>
-      <c r="CC11" s="2"/>
-      <c r="CD11" s="1"/>
-      <c r="CE11" s="1"/>
-      <c r="CF11" s="3"/>
+      <c r="BV11" s="1"/>
+      <c r="BW11" s="1"/>
+      <c r="BZ11" s="1"/>
+      <c r="CB11" s="4"/>
+      <c r="CD11" s="2"/>
+      <c r="CE11" s="2"/>
+      <c r="CF11" s="1"/>
       <c r="CG11" s="1"/>
-      <c r="CH11" s="8"/>
-      <c r="CI11" s="4"/>
-      <c r="CJ11" s="1"/>
-      <c r="CK11" s="1"/>
-      <c r="CM11" s="4"/>
-      <c r="CN11" s="3"/>
-      <c r="CO11" s="1"/>
+      <c r="CH11" s="3"/>
+      <c r="CI11" s="1"/>
+      <c r="CJ11" s="8"/>
+      <c r="CK11" s="4"/>
+      <c r="CL11" s="1"/>
+      <c r="CM11" s="1"/>
+      <c r="CO11" s="4"/>
+      <c r="CP11" s="3"/>
+      <c r="CQ11" s="1"/>
     </row>
-    <row r="12" spans="1:97" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:99">
       <c r="A12" s="1"/>
       <c r="B12" s="2"/>
       <c r="C12" s="3"/>
@@ -2345,36 +2390,38 @@
       <c r="BF12" s="4"/>
       <c r="BG12" s="1"/>
       <c r="BH12" s="1"/>
-      <c r="BI12" s="2"/>
+      <c r="BI12" s="1"/>
       <c r="BJ12" s="1"/>
-      <c r="BK12" s="1"/>
+      <c r="BK12" s="2"/>
       <c r="BL12" s="1"/>
       <c r="BM12" s="1"/>
-      <c r="BN12" s="4"/>
-      <c r="BO12" s="4"/>
-      <c r="BP12" s="1"/>
-      <c r="BQ12" s="1"/>
-      <c r="BR12" s="4"/>
+      <c r="BN12" s="1"/>
+      <c r="BO12" s="1"/>
+      <c r="BP12" s="4"/>
+      <c r="BQ12" s="4"/>
+      <c r="BR12" s="1"/>
       <c r="BS12" s="1"/>
-      <c r="BT12" s="1"/>
+      <c r="BT12" s="4"/>
       <c r="BU12" s="1"/>
-      <c r="BX12" s="1"/>
-      <c r="BZ12" s="4"/>
-      <c r="CB12" s="2"/>
-      <c r="CC12" s="2"/>
-      <c r="CD12" s="1"/>
-      <c r="CE12" s="1"/>
-      <c r="CF12" s="3"/>
+      <c r="BV12" s="1"/>
+      <c r="BW12" s="1"/>
+      <c r="BZ12" s="1"/>
+      <c r="CB12" s="4"/>
+      <c r="CD12" s="2"/>
+      <c r="CE12" s="2"/>
+      <c r="CF12" s="1"/>
       <c r="CG12" s="1"/>
-      <c r="CH12" s="8"/>
-      <c r="CI12" s="4"/>
-      <c r="CJ12" s="1"/>
-      <c r="CK12" s="1"/>
-      <c r="CM12" s="4"/>
-      <c r="CN12" s="3"/>
-      <c r="CO12" s="1"/>
+      <c r="CH12" s="3"/>
+      <c r="CI12" s="1"/>
+      <c r="CJ12" s="8"/>
+      <c r="CK12" s="4"/>
+      <c r="CL12" s="1"/>
+      <c r="CM12" s="1"/>
+      <c r="CO12" s="4"/>
+      <c r="CP12" s="3"/>
+      <c r="CQ12" s="1"/>
     </row>
-    <row r="13" spans="1:97" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:99">
       <c r="A13" s="1"/>
       <c r="B13" s="2"/>
       <c r="C13" s="3"/>
@@ -2435,34 +2482,36 @@
       <c r="BF13" s="4"/>
       <c r="BG13" s="1"/>
       <c r="BH13" s="1"/>
-      <c r="BI13" s="2"/>
+      <c r="BI13" s="1"/>
       <c r="BJ13" s="1"/>
-      <c r="BK13" s="1"/>
+      <c r="BK13" s="2"/>
       <c r="BL13" s="1"/>
       <c r="BM13" s="1"/>
-      <c r="BN13" s="4"/>
-      <c r="BO13" s="4"/>
-      <c r="BP13" s="1"/>
-      <c r="BQ13" s="1"/>
-      <c r="BR13" s="4"/>
+      <c r="BN13" s="1"/>
+      <c r="BO13" s="1"/>
+      <c r="BP13" s="4"/>
+      <c r="BQ13" s="4"/>
+      <c r="BR13" s="1"/>
       <c r="BS13" s="1"/>
-      <c r="BT13" s="1"/>
+      <c r="BT13" s="4"/>
       <c r="BU13" s="1"/>
-      <c r="BX13" s="1"/>
-      <c r="BZ13" s="4"/>
-      <c r="CB13" s="2"/>
-      <c r="CC13" s="2"/>
-      <c r="CD13" s="1"/>
-      <c r="CE13" s="1"/>
-      <c r="CF13" s="3"/>
+      <c r="BV13" s="1"/>
+      <c r="BW13" s="1"/>
+      <c r="BZ13" s="1"/>
+      <c r="CB13" s="4"/>
+      <c r="CD13" s="2"/>
+      <c r="CE13" s="2"/>
+      <c r="CF13" s="1"/>
       <c r="CG13" s="1"/>
-      <c r="CH13" s="8"/>
-      <c r="CI13" s="4"/>
-      <c r="CJ13" s="1"/>
-      <c r="CK13" s="1"/>
-      <c r="CM13" s="4"/>
-      <c r="CN13" s="3"/>
-      <c r="CO13" s="1"/>
+      <c r="CH13" s="3"/>
+      <c r="CI13" s="1"/>
+      <c r="CJ13" s="8"/>
+      <c r="CK13" s="4"/>
+      <c r="CL13" s="1"/>
+      <c r="CM13" s="1"/>
+      <c r="CO13" s="4"/>
+      <c r="CP13" s="3"/>
+      <c r="CQ13" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
